--- a/basedatos_partidas/salida/descompuestos/12.11.01.120.xlsx
+++ b/basedatos_partidas/salida/descompuestos/12.11.01.120.xlsx
@@ -558,10 +558,10 @@
         <v>0.15</v>
       </c>
       <c r="G10" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="11">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="13">
@@ -769,7 +769,7 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>4.84</v>
+        <v>4.96</v>
       </c>
       <c r="H22" t="n">
         <v>0.05</v>
@@ -788,7 +788,7 @@
       </c>
       <c r="G23" s="4" t="n"/>
       <c r="H23" s="5" t="n">
-        <v>4.89</v>
+        <v>5.01</v>
       </c>
     </row>
   </sheetData>
